--- a/01 Requirements/BRD/Feature Mapping.xlsx
+++ b/01 Requirements/BRD/Feature Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/01 Requirements/BRD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34B7B92-A8FA-AF4D-AA3D-F30FE91EBD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DE0835-55BA-3A44-9FFD-624FC53C74FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{E4B2857F-55FC-DA4A-AB72-828E9EE87AFE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{E4B2857F-55FC-DA4A-AB72-828E9EE87AFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
   <si>
     <t>Req Id</t>
   </si>
@@ -283,6 +283,57 @@
   </si>
   <si>
     <t>Review programs</t>
+  </si>
+  <si>
+    <t>Create Cohort</t>
+  </si>
+  <si>
+    <t>Initiation</t>
+  </si>
+  <si>
+    <t>Request Management</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
+    <t>Change Management</t>
+  </si>
+  <si>
+    <t>Action and Dependency Management</t>
+  </si>
+  <si>
+    <t>Vendor Management</t>
+  </si>
+  <si>
+    <t>Business Partner</t>
+  </si>
+  <si>
+    <t>View Projects</t>
+  </si>
+  <si>
+    <t>-Can view list of demands</t>
+  </si>
+  <si>
+    <t>Request needs to be generated before Initiation</t>
+  </si>
+  <si>
+    <t>-Can create Projects D43₹</t>
+  </si>
+  <si>
+    <t>-Update VCF</t>
+  </si>
+  <si>
+    <t>Needs to be created previously</t>
+  </si>
+  <si>
+    <t>Update VCF</t>
+  </si>
+  <si>
+    <t>Business Partner manager</t>
   </si>
 </sst>
 </file>
@@ -794,10 +845,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D607A7C-00D7-D24E-B0BF-4C14448699DE}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23" style="2" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.1640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="36.5" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -1057,6 +1108,9 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C28" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="D28" s="6" t="s">
         <v>66</v>
       </c>
@@ -1118,9 +1172,77 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D42" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/01 Requirements/BRD/Feature Mapping.xlsx
+++ b/01 Requirements/BRD/Feature Mapping.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/01 Requirements/BRD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DE0835-55BA-3A44-9FFD-624FC53C74FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519EB245-EFF9-4D41-8116-2B5280006DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{E4B2857F-55FC-DA4A-AB72-828E9EE87AFE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" activeTab="2" xr2:uid="{E4B2857F-55FC-DA4A-AB72-828E9EE87AFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Feature Mapping" sheetId="2" r:id="rId2"/>
+    <sheet name="Initiation Tables" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="350">
   <si>
     <t>Req Id</t>
   </si>
@@ -315,32 +317,797 @@
     <t>View Projects</t>
   </si>
   <si>
-    <t>-Can view list of demands</t>
-  </si>
-  <si>
-    <t>Request needs to be generated before Initiation</t>
-  </si>
-  <si>
-    <t>-Can create Projects D43₹</t>
-  </si>
-  <si>
-    <t>-Update VCF</t>
-  </si>
-  <si>
-    <t>Needs to be created previously</t>
-  </si>
-  <si>
     <t>Update VCF</t>
   </si>
   <si>
-    <t>Business Partner manager</t>
+    <t>Create Program</t>
+  </si>
+  <si>
+    <t>Create VCF</t>
+  </si>
+  <si>
+    <t>Create VCF against a Program</t>
+  </si>
+  <si>
+    <t>-Create Projects against a Demand ID</t>
+  </si>
+  <si>
+    <t>-View list of demands</t>
+  </si>
+  <si>
+    <t>-Update VCF against a Program ID</t>
+  </si>
+  <si>
+    <t>Create Projects</t>
+  </si>
+  <si>
+    <t>Business Partner Manager</t>
+  </si>
+  <si>
+    <t>Demand needs to be generated before Initiation</t>
+  </si>
+  <si>
+    <t>Needs to be created previously from a program</t>
+  </si>
+  <si>
+    <t>View fields are different than  41</t>
+  </si>
+  <si>
+    <t>Approve Projects</t>
+  </si>
+  <si>
+    <t>Approve Project</t>
+  </si>
+  <si>
+    <t>Governance Head</t>
+  </si>
+  <si>
+    <t>-View list of Programs</t>
+  </si>
+  <si>
+    <t>-View list of Projects</t>
+  </si>
+  <si>
+    <t>Assign Project Manager</t>
+  </si>
+  <si>
+    <t>Assign Project Manager for Approved Project</t>
+  </si>
+  <si>
+    <t>Business User</t>
+  </si>
+  <si>
+    <t>-View list of Approved Projects</t>
+  </si>
+  <si>
+    <t>Upload BRD</t>
+  </si>
+  <si>
+    <t>Upload BRD against a project</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>PK/FK</t>
+  </si>
+  <si>
+    <t>Mandatory</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>demand_id</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Unique identifier for demand</t>
+  </si>
+  <si>
+    <t>demand_title</t>
+  </si>
+  <si>
+    <t>VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>Title of the demand</t>
+  </si>
+  <si>
+    <t>demand_description</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Description of demand</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>VARCHAR(30)</t>
+  </si>
+  <si>
+    <t>Demand status</t>
+  </si>
+  <si>
+    <t>created_by</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <t>User who created demand</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>Demand creation timestamp</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>program_id</t>
+  </si>
+  <si>
+    <t>program_name</t>
+  </si>
+  <si>
+    <t>program_description</t>
+  </si>
+  <si>
+    <t>Program creation timestamp</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>project_id</t>
+  </si>
+  <si>
+    <t>Unique project identifier</t>
+  </si>
+  <si>
+    <t>Demand from which project is created</t>
+  </si>
+  <si>
+    <t>Program associated with project</t>
+  </si>
+  <si>
+    <t>project_name</t>
+  </si>
+  <si>
+    <t>Project name</t>
+  </si>
+  <si>
+    <t>project_type</t>
+  </si>
+  <si>
+    <t>Project type (POC, etc.)</t>
+  </si>
+  <si>
+    <t>expected_start_date</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>Expected project start date</t>
+  </si>
+  <si>
+    <t>expected_end_date</t>
+  </si>
+  <si>
+    <t>Expected project end date</t>
+  </si>
+  <si>
+    <t>budget_amount</t>
+  </si>
+  <si>
+    <t>DECIMAL(15,2)</t>
+  </si>
+  <si>
+    <t>Budget allocated for project</t>
+  </si>
+  <si>
+    <t>budget_currency</t>
+  </si>
+  <si>
+    <t>VARCHAR(10)</t>
+  </si>
+  <si>
+    <t>Currency for project budget</t>
+  </si>
+  <si>
+    <t>Current project status</t>
+  </si>
+  <si>
+    <t>manpower_estimate_id</t>
+  </si>
+  <si>
+    <t>Fk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill </t>
+  </si>
+  <si>
+    <t>User who created project</t>
+  </si>
+  <si>
+    <t>Project creation timestamp</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>Last update timestamp</t>
+  </si>
+  <si>
+    <t>VCF</t>
+  </si>
+  <si>
+    <t>version_no</t>
+  </si>
+  <si>
+    <t>updated_by</t>
+  </si>
+  <si>
+    <t>Manpower_Estimate</t>
+  </si>
+  <si>
+    <t>Unique manpower estimate record</t>
+  </si>
+  <si>
+    <t>Project associated with manpower estimate</t>
+  </si>
+  <si>
+    <t>skillset</t>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+  </si>
+  <si>
+    <t>Skillset required</t>
+  </si>
+  <si>
+    <t>headcount</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>Number of resources required</t>
+  </si>
+  <si>
+    <t>utilization_percentage</t>
+  </si>
+  <si>
+    <t>DECIMAL(5,2)</t>
+  </si>
+  <si>
+    <t>Utilization percentage</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>Resource start date</t>
+  </si>
+  <si>
+    <t>end_date</t>
+  </si>
+  <si>
+    <t>Resource end date</t>
+  </si>
+  <si>
+    <t>remarks</t>
+  </si>
+  <si>
+    <t>Additional comments</t>
+  </si>
+  <si>
+    <t>Creation timestamp</t>
+  </si>
+  <si>
+    <t>Project_Approval</t>
+  </si>
+  <si>
+    <t>approval_id</t>
+  </si>
+  <si>
+    <t>Unique approval record</t>
+  </si>
+  <si>
+    <t>Project being approved</t>
+  </si>
+  <si>
+    <t>approver_user_id</t>
+  </si>
+  <si>
+    <t>User performing approval</t>
+  </si>
+  <si>
+    <t>approver_role</t>
+  </si>
+  <si>
+    <t>Role of approver</t>
+  </si>
+  <si>
+    <t>approval_stage</t>
+  </si>
+  <si>
+    <t>Stage in approval workflow</t>
+  </si>
+  <si>
+    <t>approval_status</t>
+  </si>
+  <si>
+    <t>Approved / Rejected / Pending</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>Comments from approver</t>
+  </si>
+  <si>
+    <t>action_at</t>
+  </si>
+  <si>
+    <t>Timestamp of approval action</t>
+  </si>
+  <si>
+    <t>Unique identifier for the program</t>
+  </si>
+  <si>
+    <t>Demand ID from which the program is created (auto populated, non-editable)</t>
+  </si>
+  <si>
+    <t>Name of the program</t>
+  </si>
+  <si>
+    <t>Detailed description of the program</t>
+  </si>
+  <si>
+    <t>program_start_year</t>
+  </si>
+  <si>
+    <t>YEAR / INT</t>
+  </si>
+  <si>
+    <t>Year in which the program starts</t>
+  </si>
+  <si>
+    <t>program_type</t>
+  </si>
+  <si>
+    <t>Type of program (Software / Non-Software)</t>
+  </si>
+  <si>
+    <t>ownership_type</t>
+  </si>
+  <si>
+    <t>Ownership of program (Business / DE)</t>
+  </si>
+  <si>
+    <t>business_spoc_id</t>
+  </si>
+  <si>
+    <t>Employee ID of Business SPOC selected from HRMS</t>
+  </si>
+  <si>
+    <t>business_vertical</t>
+  </si>
+  <si>
+    <t>Business vertical auto-populated based on selected employee</t>
+  </si>
+  <si>
+    <t>investment_category</t>
+  </si>
+  <si>
+    <t>Investment category (Mega / High / Medium / Low)</t>
+  </si>
+  <si>
+    <t>program_classification</t>
+  </si>
+  <si>
+    <t>Classification of program (Enterprise Transformation / Efficiency Tool / Essential / Established Technologies / Experimental)</t>
+  </si>
+  <si>
+    <t>program_de_pillar_id</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>DE Pillar ID</t>
+  </si>
+  <si>
+    <t>User who created the program</t>
+  </si>
+  <si>
+    <t>Last user who updated program</t>
+  </si>
+  <si>
+    <t>Program_DE_Pillar</t>
+  </si>
+  <si>
+    <t>Unique record identifier</t>
+  </si>
+  <si>
+    <t>Program to which DE pillar is associated</t>
+  </si>
+  <si>
+    <t>de_pillar</t>
+  </si>
+  <si>
+    <t>Program ID to which this VCF belongs</t>
+  </si>
+  <si>
+    <t>Status of VCF (Draft / Submitted / Approved / Archived)</t>
+  </si>
+  <si>
+    <t>effective_year</t>
+  </si>
+  <si>
+    <t>Starting financial/planning year for the VCF</t>
+  </si>
+  <si>
+    <t>npv</t>
+  </si>
+  <si>
+    <t>DECIMAL(18,2)</t>
+  </si>
+  <si>
+    <t>Net Present Value derived from VCF framework</t>
+  </si>
+  <si>
+    <t>irr</t>
+  </si>
+  <si>
+    <t>DECIMAL(7,2)</t>
+  </si>
+  <si>
+    <t>Internal Rate of Return derived from VCF framework</t>
+  </si>
+  <si>
+    <t>User who created the VCF version</t>
+  </si>
+  <si>
+    <t>User who last updated the VCF</t>
+  </si>
+  <si>
+    <t>VARCHAR(500)</t>
+  </si>
+  <si>
+    <t>General remarks/comments for the VCF</t>
+  </si>
+  <si>
+    <t>VCF_Value_Lever</t>
+  </si>
+  <si>
+    <t>value_lever_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for a value lever</t>
+  </si>
+  <si>
+    <t>lever_name</t>
+  </si>
+  <si>
+    <t>Name of the value lever</t>
+  </si>
+  <si>
+    <t>display_order</t>
+  </si>
+  <si>
+    <t>Sequence/order in which the lever is shown</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <t>Indicates whether the lever is active in this version</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>Year-wise amount/value for the lever</t>
+  </si>
+  <si>
+    <t>VCF_Cost_Lever</t>
+  </si>
+  <si>
+    <t>cost_lever_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for a cost lever</t>
+  </si>
+  <si>
+    <t>Name of the cost lever</t>
+  </si>
+  <si>
+    <t>Indicates whether the cost lever is active in this version</t>
+  </si>
+  <si>
+    <t>VCF_Version_History</t>
+  </si>
+  <si>
+    <t>history_id</t>
+  </si>
+  <si>
+    <t>Unique identifier for version history record</t>
+  </si>
+  <si>
+    <t>Version number</t>
+  </si>
+  <si>
+    <t>change_summary</t>
+  </si>
+  <si>
+    <t>Summary of changes made in this version</t>
+  </si>
+  <si>
+    <t>changed_by</t>
+  </si>
+  <si>
+    <t>User who made the change</t>
+  </si>
+  <si>
+    <t>changed_at</t>
+  </si>
+  <si>
+    <t>Timestamp of change</t>
+  </si>
+  <si>
+    <t>Cost_lever_name</t>
+  </si>
+  <si>
+    <t>DE pillar value one or many from (A / B / C / D / E)</t>
+  </si>
+  <si>
+    <t>project_status</t>
+  </si>
+  <si>
+    <t>Business lifecycle status of project</t>
+  </si>
+  <si>
+    <t>is_approved</t>
+  </si>
+  <si>
+    <t>Indicates whether project is finally approved</t>
+  </si>
+  <si>
+    <t>program_status</t>
+  </si>
+  <si>
+    <t>Approval_Workflow_Step</t>
+  </si>
+  <si>
+    <t>workflow_step_id</t>
+  </si>
+  <si>
+    <t>Unique workflow step record</t>
+  </si>
+  <si>
+    <t>entity_type</t>
+  </si>
+  <si>
+    <t>PROJECT or PROGRAM</t>
+  </si>
+  <si>
+    <t>entity_id</t>
+  </si>
+  <si>
+    <t>Project ID or Program ID</t>
+  </si>
+  <si>
+    <t>stage_code</t>
+  </si>
+  <si>
+    <t>Approval stage code</t>
+  </si>
+  <si>
+    <t>Actual approver</t>
+  </si>
+  <si>
+    <t>step_status</t>
+  </si>
+  <si>
+    <t>PENDING / APPROVED / REJECTED / SENT_BACK</t>
+  </si>
+  <si>
+    <t>Approver remarks</t>
+  </si>
+  <si>
+    <t>sequence_no</t>
+  </si>
+  <si>
+    <t>Sequence of stage</t>
+  </si>
+  <si>
+    <t>Approval_Status_Master</t>
+  </si>
+  <si>
+    <t>approval_status_code</t>
+  </si>
+  <si>
+    <t>Unique code for approval status</t>
+  </si>
+  <si>
+    <t>approval_status_name</t>
+  </si>
+  <si>
+    <t>Display name of approval status</t>
+  </si>
+  <si>
+    <t>Indicates whether status is active</t>
+  </si>
+  <si>
+    <t>NOT_SUBMITTED</t>
+  </si>
+  <si>
+    <t>Not Submitted</t>
+  </si>
+  <si>
+    <t>IN_APPROVAL</t>
+  </si>
+  <si>
+    <t>In Approval</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>SENT_BACK</t>
+  </si>
+  <si>
+    <t>Sent Back</t>
+  </si>
+  <si>
+    <t>CANCELLED</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>WITHDRAWN</t>
+  </si>
+  <si>
+    <t>Withdrawn</t>
+  </si>
+  <si>
+    <t>Suggested Values</t>
+  </si>
+  <si>
+    <t>Approval_Stage_Master</t>
+  </si>
+  <si>
+    <t>Unique code for approval stage</t>
+  </si>
+  <si>
+    <t>stage_name</t>
+  </si>
+  <si>
+    <t>Display name of approval stage</t>
+  </si>
+  <si>
+    <t>Indicates whether stage is active</t>
+  </si>
+  <si>
+    <t>BP_DRAFT</t>
+  </si>
+  <si>
+    <t>Draft by Business Partner</t>
+  </si>
+  <si>
+    <t>BPM_APPROVAL</t>
+  </si>
+  <si>
+    <t>Business Partner Manager Approval</t>
+  </si>
+  <si>
+    <t>GOV_APPROVAL</t>
+  </si>
+  <si>
+    <t>Governance Head Approval</t>
+  </si>
+  <si>
+    <t>COE_APPROVAL</t>
+  </si>
+  <si>
+    <t>CoE Head Approval</t>
+  </si>
+  <si>
+    <t>FINAL_APPROVED</t>
+  </si>
+  <si>
+    <t>Final Approved</t>
+  </si>
+  <si>
+    <t>Approval_Status_code</t>
+  </si>
+  <si>
+    <t>Approval_stage_Code</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Feature Details</t>
+  </si>
+  <si>
+    <t>Demand Service</t>
+  </si>
+  <si>
+    <t>Demand query, demand validation, demand details retrieval</t>
+  </si>
+  <si>
+    <t>Mostly read-heavy in this initiation scope</t>
+  </si>
+  <si>
+    <t>Program Service</t>
+  </si>
+  <si>
+    <t>Create/update/read program, maintain program status summary</t>
+  </si>
+  <si>
+    <t>Owns Program master data</t>
+  </si>
+  <si>
+    <t>Project Service</t>
+  </si>
+  <si>
+    <t>Create/update/read project, maintain project status summary, PM assignment reference</t>
+  </si>
+  <si>
+    <t>Owns Project master data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -382,6 +1149,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -410,7 +1185,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -436,6 +1211,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -845,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D607A7C-00D7-D24E-B0BF-4C14448699DE}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -1187,61 +1963,269 @@
         <v>79</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="2">
+        <v>52</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D42" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="2">
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C43" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="2">
+        <v>54</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>92</v>
+      <c r="F46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="2">
+        <v>59</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B49" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B51" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C52" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G52" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C53" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B54" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C55" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" s="8" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="8"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="8"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="8"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="8"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="8"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" s="8" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="8" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" s="8" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="8" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" s="8" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1251,4 +2235,2541 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F193F0A-FA0B-D541-914E-6262846BAE7B}">
+  <dimension ref="B2:O155"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="35" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" t="s">
+        <v>154</v>
+      </c>
+      <c r="F17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" t="s">
+        <v>337</v>
+      </c>
+      <c r="D23" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" t="s">
+        <v>134</v>
+      </c>
+      <c r="F31" t="s">
+        <v>120</v>
+      </c>
+      <c r="G31" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33" t="s">
+        <v>120</v>
+      </c>
+      <c r="G33" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" t="s">
+        <v>185</v>
+      </c>
+      <c r="F34" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G38" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" t="s">
+        <v>119</v>
+      </c>
+      <c r="F41" t="s">
+        <v>120</v>
+      </c>
+      <c r="G41" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D42" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" t="s">
+        <v>120</v>
+      </c>
+      <c r="G42" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" t="s">
+        <v>120</v>
+      </c>
+      <c r="G43" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" t="s">
+        <v>200</v>
+      </c>
+      <c r="D44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
+        <v>120</v>
+      </c>
+      <c r="G44" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>194</v>
+      </c>
+      <c r="C45" t="s">
+        <v>202</v>
+      </c>
+      <c r="D45" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" t="s">
+        <v>120</v>
+      </c>
+      <c r="G45" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>194</v>
+      </c>
+      <c r="C46" t="s">
+        <v>204</v>
+      </c>
+      <c r="D46" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" t="s">
+        <v>120</v>
+      </c>
+      <c r="G46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47" t="s">
+        <v>206</v>
+      </c>
+      <c r="D47" t="s">
+        <v>123</v>
+      </c>
+      <c r="F47" t="s">
+        <v>127</v>
+      </c>
+      <c r="G47" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>194</v>
+      </c>
+      <c r="C48" t="s">
+        <v>208</v>
+      </c>
+      <c r="D48" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" t="s">
+        <v>120</v>
+      </c>
+      <c r="G48" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" t="s">
+        <v>119</v>
+      </c>
+      <c r="F51" t="s">
+        <v>120</v>
+      </c>
+      <c r="G51" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" t="s">
+        <v>134</v>
+      </c>
+      <c r="F52" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" t="s">
+        <v>123</v>
+      </c>
+      <c r="F53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>139</v>
+      </c>
+      <c r="C54" t="s">
+        <v>142</v>
+      </c>
+      <c r="D54" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" t="s">
+        <v>120</v>
+      </c>
+      <c r="G54" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" t="s">
+        <v>214</v>
+      </c>
+      <c r="D55" t="s">
+        <v>215</v>
+      </c>
+      <c r="F55" t="s">
+        <v>120</v>
+      </c>
+      <c r="G55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" t="s">
+        <v>217</v>
+      </c>
+      <c r="D56" t="s">
+        <v>133</v>
+      </c>
+      <c r="F56" t="s">
+        <v>120</v>
+      </c>
+      <c r="G56" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" t="s">
+        <v>219</v>
+      </c>
+      <c r="D57" t="s">
+        <v>133</v>
+      </c>
+      <c r="F57" t="s">
+        <v>120</v>
+      </c>
+      <c r="G57" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" t="s">
+        <v>221</v>
+      </c>
+      <c r="D58" t="s">
+        <v>133</v>
+      </c>
+      <c r="E58" t="s">
+        <v>134</v>
+      </c>
+      <c r="F58" t="s">
+        <v>120</v>
+      </c>
+      <c r="G58" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" t="s">
+        <v>223</v>
+      </c>
+      <c r="D59" t="s">
+        <v>179</v>
+      </c>
+      <c r="F59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G59" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" t="s">
+        <v>225</v>
+      </c>
+      <c r="D60" t="s">
+        <v>133</v>
+      </c>
+      <c r="F60" t="s">
+        <v>120</v>
+      </c>
+      <c r="G60" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" t="s">
+        <v>227</v>
+      </c>
+      <c r="D61" t="s">
+        <v>179</v>
+      </c>
+      <c r="F61" t="s">
+        <v>120</v>
+      </c>
+      <c r="G61" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" t="s">
+        <v>229</v>
+      </c>
+      <c r="D62" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" t="s">
+        <v>166</v>
+      </c>
+      <c r="F62" t="s">
+        <v>230</v>
+      </c>
+      <c r="G62" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" t="s">
+        <v>285</v>
+      </c>
+      <c r="D63" t="s">
+        <v>130</v>
+      </c>
+      <c r="F63" t="s">
+        <v>120</v>
+      </c>
+      <c r="G63" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" t="s">
+        <v>337</v>
+      </c>
+      <c r="D64" t="s">
+        <v>130</v>
+      </c>
+      <c r="E64" t="s">
+        <v>166</v>
+      </c>
+      <c r="F64" t="s">
+        <v>120</v>
+      </c>
+      <c r="G64" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" t="s">
+        <v>338</v>
+      </c>
+      <c r="D65" t="s">
+        <v>133</v>
+      </c>
+      <c r="E65" t="s">
+        <v>134</v>
+      </c>
+      <c r="F65" t="s">
+        <v>120</v>
+      </c>
+      <c r="G65" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" t="s">
+        <v>283</v>
+      </c>
+      <c r="D66" t="s">
+        <v>260</v>
+      </c>
+      <c r="F66" t="s">
+        <v>120</v>
+      </c>
+      <c r="G66" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" t="s">
+        <v>132</v>
+      </c>
+      <c r="D67" t="s">
+        <v>133</v>
+      </c>
+      <c r="F67" t="s">
+        <v>120</v>
+      </c>
+      <c r="G67" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>139</v>
+      </c>
+      <c r="C68" t="s">
+        <v>136</v>
+      </c>
+      <c r="D68" t="s">
+        <v>137</v>
+      </c>
+      <c r="F68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G68" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" t="s">
+        <v>133</v>
+      </c>
+      <c r="F69" t="s">
+        <v>127</v>
+      </c>
+      <c r="G69" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" t="s">
+        <v>170</v>
+      </c>
+      <c r="D70" t="s">
+        <v>137</v>
+      </c>
+      <c r="F70" t="s">
+        <v>127</v>
+      </c>
+      <c r="G70" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B72" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>234</v>
+      </c>
+      <c r="C73" t="s">
+        <v>229</v>
+      </c>
+      <c r="D73" t="s">
+        <v>118</v>
+      </c>
+      <c r="E73" t="s">
+        <v>119</v>
+      </c>
+      <c r="F73" t="s">
+        <v>120</v>
+      </c>
+      <c r="G73" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74" t="s">
+        <v>140</v>
+      </c>
+      <c r="D74" t="s">
+        <v>118</v>
+      </c>
+      <c r="E74" t="s">
+        <v>134</v>
+      </c>
+      <c r="F74" t="s">
+        <v>120</v>
+      </c>
+      <c r="G74" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>234</v>
+      </c>
+      <c r="C75" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" t="s">
+        <v>118</v>
+      </c>
+      <c r="F75" t="s">
+        <v>120</v>
+      </c>
+      <c r="G75" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B78" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B79" t="s">
+        <v>172</v>
+      </c>
+      <c r="C79" t="s">
+        <v>140</v>
+      </c>
+      <c r="D79" t="s">
+        <v>118</v>
+      </c>
+      <c r="E79" t="s">
+        <v>119</v>
+      </c>
+      <c r="F79" t="s">
+        <v>120</v>
+      </c>
+      <c r="G79" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>172</v>
+      </c>
+      <c r="C80" t="s">
+        <v>253</v>
+      </c>
+      <c r="D80" t="s">
+        <v>118</v>
+      </c>
+      <c r="E80" t="s">
+        <v>134</v>
+      </c>
+      <c r="F80" t="s">
+        <v>120</v>
+      </c>
+      <c r="G80" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>172</v>
+      </c>
+      <c r="C81" t="s">
+        <v>265</v>
+      </c>
+      <c r="D81" t="s">
+        <v>118</v>
+      </c>
+      <c r="E81" t="s">
+        <v>134</v>
+      </c>
+      <c r="F81" t="s">
+        <v>120</v>
+      </c>
+      <c r="G81" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" t="s">
+        <v>129</v>
+      </c>
+      <c r="D82" t="s">
+        <v>130</v>
+      </c>
+      <c r="F82" t="s">
+        <v>120</v>
+      </c>
+      <c r="G82" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
+        <v>172</v>
+      </c>
+      <c r="C83" t="s">
+        <v>242</v>
+      </c>
+      <c r="D83" t="s">
+        <v>243</v>
+      </c>
+      <c r="F83" t="s">
+        <v>127</v>
+      </c>
+      <c r="G83" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>172</v>
+      </c>
+      <c r="C84" t="s">
+        <v>245</v>
+      </c>
+      <c r="D84" t="s">
+        <v>246</v>
+      </c>
+      <c r="F84" t="s">
+        <v>127</v>
+      </c>
+      <c r="G84" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B85" t="s">
+        <v>172</v>
+      </c>
+      <c r="C85" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85" t="s">
+        <v>133</v>
+      </c>
+      <c r="F85" t="s">
+        <v>120</v>
+      </c>
+      <c r="G85" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>172</v>
+      </c>
+      <c r="C86" t="s">
+        <v>136</v>
+      </c>
+      <c r="D86" t="s">
+        <v>137</v>
+      </c>
+      <c r="F86" t="s">
+        <v>120</v>
+      </c>
+      <c r="G86" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B87" t="s">
+        <v>172</v>
+      </c>
+      <c r="C87" t="s">
+        <v>174</v>
+      </c>
+      <c r="D87" t="s">
+        <v>133</v>
+      </c>
+      <c r="F87" t="s">
+        <v>127</v>
+      </c>
+      <c r="G87" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B88" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88" t="s">
+        <v>170</v>
+      </c>
+      <c r="D88" t="s">
+        <v>137</v>
+      </c>
+      <c r="F88" t="s">
+        <v>127</v>
+      </c>
+      <c r="G88" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B89" t="s">
+        <v>172</v>
+      </c>
+      <c r="C89" t="s">
+        <v>191</v>
+      </c>
+      <c r="D89" t="s">
+        <v>250</v>
+      </c>
+      <c r="F89" t="s">
+        <v>127</v>
+      </c>
+      <c r="G89" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B92" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B93" t="s">
+        <v>252</v>
+      </c>
+      <c r="C93" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" t="s">
+        <v>118</v>
+      </c>
+      <c r="E93" t="s">
+        <v>134</v>
+      </c>
+      <c r="F93" t="s">
+        <v>120</v>
+      </c>
+      <c r="G93" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B94" t="s">
+        <v>252</v>
+      </c>
+      <c r="C94" t="s">
+        <v>253</v>
+      </c>
+      <c r="D94" t="s">
+        <v>118</v>
+      </c>
+      <c r="E94" t="s">
+        <v>119</v>
+      </c>
+      <c r="F94" t="s">
+        <v>120</v>
+      </c>
+      <c r="G94" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B95" t="s">
+        <v>252</v>
+      </c>
+      <c r="C95" t="s">
+        <v>240</v>
+      </c>
+      <c r="D95" t="s">
+        <v>182</v>
+      </c>
+      <c r="F95" t="s">
+        <v>127</v>
+      </c>
+      <c r="G95" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B96" t="s">
+        <v>252</v>
+      </c>
+      <c r="C96" t="s">
+        <v>255</v>
+      </c>
+      <c r="D96" t="s">
+        <v>123</v>
+      </c>
+      <c r="F96" t="s">
+        <v>120</v>
+      </c>
+      <c r="G96" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B97" t="s">
+        <v>252</v>
+      </c>
+      <c r="C97" t="s">
+        <v>262</v>
+      </c>
+      <c r="D97" t="s">
+        <v>243</v>
+      </c>
+      <c r="F97" t="s">
+        <v>127</v>
+      </c>
+      <c r="G97" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B98" t="s">
+        <v>252</v>
+      </c>
+      <c r="C98" t="s">
+        <v>257</v>
+      </c>
+      <c r="D98" t="s">
+        <v>182</v>
+      </c>
+      <c r="F98" t="s">
+        <v>127</v>
+      </c>
+      <c r="G98" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B99" t="s">
+        <v>252</v>
+      </c>
+      <c r="C99" t="s">
+        <v>259</v>
+      </c>
+      <c r="D99" t="s">
+        <v>260</v>
+      </c>
+      <c r="F99" t="s">
+        <v>120</v>
+      </c>
+      <c r="G99" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B100" t="s">
+        <v>252</v>
+      </c>
+      <c r="C100" t="s">
+        <v>136</v>
+      </c>
+      <c r="D100" t="s">
+        <v>137</v>
+      </c>
+      <c r="F100" t="s">
+        <v>120</v>
+      </c>
+      <c r="G100" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B101" t="s">
+        <v>252</v>
+      </c>
+      <c r="C101" t="s">
+        <v>170</v>
+      </c>
+      <c r="D101" t="s">
+        <v>137</v>
+      </c>
+      <c r="F101" t="s">
+        <v>127</v>
+      </c>
+      <c r="G101" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B105" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B106" t="s">
+        <v>264</v>
+      </c>
+      <c r="C106" t="s">
+        <v>140</v>
+      </c>
+      <c r="D106" t="s">
+        <v>118</v>
+      </c>
+      <c r="E106" t="s">
+        <v>134</v>
+      </c>
+      <c r="F106" t="s">
+        <v>120</v>
+      </c>
+      <c r="G106" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B107" t="s">
+        <v>264</v>
+      </c>
+      <c r="C107" t="s">
+        <v>265</v>
+      </c>
+      <c r="D107" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107" t="s">
+        <v>119</v>
+      </c>
+      <c r="F107" t="s">
+        <v>120</v>
+      </c>
+      <c r="G107" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B108" t="s">
+        <v>264</v>
+      </c>
+      <c r="C108" t="s">
+        <v>240</v>
+      </c>
+      <c r="D108" t="s">
+        <v>182</v>
+      </c>
+      <c r="F108" t="s">
+        <v>127</v>
+      </c>
+      <c r="G108" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B109" t="s">
+        <v>264</v>
+      </c>
+      <c r="C109" t="s">
+        <v>279</v>
+      </c>
+      <c r="D109" t="s">
+        <v>123</v>
+      </c>
+      <c r="F109" t="s">
+        <v>120</v>
+      </c>
+      <c r="G109" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B110" t="s">
+        <v>252</v>
+      </c>
+      <c r="C110" t="s">
+        <v>262</v>
+      </c>
+      <c r="D110" t="s">
+        <v>243</v>
+      </c>
+      <c r="F110" t="s">
+        <v>127</v>
+      </c>
+      <c r="G110" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B111" t="s">
+        <v>264</v>
+      </c>
+      <c r="C111" t="s">
+        <v>257</v>
+      </c>
+      <c r="D111" t="s">
+        <v>182</v>
+      </c>
+      <c r="F111" t="s">
+        <v>127</v>
+      </c>
+      <c r="G111" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B112" t="s">
+        <v>264</v>
+      </c>
+      <c r="C112" t="s">
+        <v>259</v>
+      </c>
+      <c r="D112" t="s">
+        <v>260</v>
+      </c>
+      <c r="F112" t="s">
+        <v>120</v>
+      </c>
+      <c r="G112" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B113" t="s">
+        <v>264</v>
+      </c>
+      <c r="C113" t="s">
+        <v>136</v>
+      </c>
+      <c r="D113" t="s">
+        <v>137</v>
+      </c>
+      <c r="F113" t="s">
+        <v>120</v>
+      </c>
+      <c r="G113" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B114" t="s">
+        <v>264</v>
+      </c>
+      <c r="C114" t="s">
+        <v>170</v>
+      </c>
+      <c r="D114" t="s">
+        <v>137</v>
+      </c>
+      <c r="F114" t="s">
+        <v>127</v>
+      </c>
+      <c r="G114" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B117" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B118" t="s">
+        <v>269</v>
+      </c>
+      <c r="C118" t="s">
+        <v>270</v>
+      </c>
+      <c r="D118" t="s">
+        <v>118</v>
+      </c>
+      <c r="E118" t="s">
+        <v>119</v>
+      </c>
+      <c r="F118" t="s">
+        <v>120</v>
+      </c>
+      <c r="G118" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B119" t="s">
+        <v>269</v>
+      </c>
+      <c r="C119" t="s">
+        <v>253</v>
+      </c>
+      <c r="D119" t="s">
+        <v>118</v>
+      </c>
+      <c r="E119" t="s">
+        <v>119</v>
+      </c>
+      <c r="F119" t="s">
+        <v>120</v>
+      </c>
+      <c r="G119" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B120" t="s">
+        <v>269</v>
+      </c>
+      <c r="C120" t="s">
+        <v>265</v>
+      </c>
+      <c r="D120" t="s">
+        <v>118</v>
+      </c>
+      <c r="E120" t="s">
+        <v>119</v>
+      </c>
+      <c r="F120" t="s">
+        <v>120</v>
+      </c>
+      <c r="G120" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B121" t="s">
+        <v>269</v>
+      </c>
+      <c r="C121" t="s">
+        <v>173</v>
+      </c>
+      <c r="D121" t="s">
+        <v>182</v>
+      </c>
+      <c r="F121" t="s">
+        <v>120</v>
+      </c>
+      <c r="G121" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B122" t="s">
+        <v>269</v>
+      </c>
+      <c r="C122" t="s">
+        <v>273</v>
+      </c>
+      <c r="D122" t="s">
+        <v>250</v>
+      </c>
+      <c r="F122" t="s">
+        <v>127</v>
+      </c>
+      <c r="G122" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B123" t="s">
+        <v>269</v>
+      </c>
+      <c r="C123" t="s">
+        <v>275</v>
+      </c>
+      <c r="D123" t="s">
+        <v>133</v>
+      </c>
+      <c r="E123" t="s">
+        <v>134</v>
+      </c>
+      <c r="F123" t="s">
+        <v>120</v>
+      </c>
+      <c r="G123" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B124" t="s">
+        <v>269</v>
+      </c>
+      <c r="C124" t="s">
+        <v>277</v>
+      </c>
+      <c r="D124" t="s">
+        <v>137</v>
+      </c>
+      <c r="F124" t="s">
+        <v>120</v>
+      </c>
+      <c r="G124" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B127" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B128" t="s">
+        <v>286</v>
+      </c>
+      <c r="C128" t="s">
+        <v>287</v>
+      </c>
+      <c r="D128" t="s">
+        <v>118</v>
+      </c>
+      <c r="E128" t="s">
+        <v>119</v>
+      </c>
+      <c r="F128" t="s">
+        <v>120</v>
+      </c>
+      <c r="G128" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="129" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B129" t="s">
+        <v>286</v>
+      </c>
+      <c r="C129" t="s">
+        <v>289</v>
+      </c>
+      <c r="D129" t="s">
+        <v>118</v>
+      </c>
+      <c r="F129" t="s">
+        <v>120</v>
+      </c>
+      <c r="G129" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="130" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B130" t="s">
+        <v>286</v>
+      </c>
+      <c r="C130" t="s">
+        <v>291</v>
+      </c>
+      <c r="D130" t="s">
+        <v>118</v>
+      </c>
+      <c r="F130" t="s">
+        <v>120</v>
+      </c>
+      <c r="G130" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="131" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
+        <v>286</v>
+      </c>
+      <c r="C131" t="s">
+        <v>293</v>
+      </c>
+      <c r="D131" t="s">
+        <v>133</v>
+      </c>
+      <c r="E131" t="s">
+        <v>134</v>
+      </c>
+      <c r="F131" t="s">
+        <v>120</v>
+      </c>
+      <c r="G131" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="132" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B132" t="s">
+        <v>286</v>
+      </c>
+      <c r="C132" t="s">
+        <v>198</v>
+      </c>
+      <c r="D132" t="s">
+        <v>133</v>
+      </c>
+      <c r="E132" t="s">
+        <v>134</v>
+      </c>
+      <c r="F132" t="s">
+        <v>120</v>
+      </c>
+      <c r="G132" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="133" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B133" t="s">
+        <v>286</v>
+      </c>
+      <c r="C133" t="s">
+        <v>296</v>
+      </c>
+      <c r="D133" t="s">
+        <v>130</v>
+      </c>
+      <c r="F133" t="s">
+        <v>120</v>
+      </c>
+      <c r="G133" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="134" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B134" t="s">
+        <v>286</v>
+      </c>
+      <c r="C134" t="s">
+        <v>206</v>
+      </c>
+      <c r="D134" t="s">
+        <v>250</v>
+      </c>
+      <c r="F134" t="s">
+        <v>127</v>
+      </c>
+      <c r="G134" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="135" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B135" t="s">
+        <v>286</v>
+      </c>
+      <c r="C135" t="s">
+        <v>208</v>
+      </c>
+      <c r="D135" t="s">
+        <v>137</v>
+      </c>
+      <c r="F135" t="s">
+        <v>127</v>
+      </c>
+      <c r="G135" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="136" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B136" t="s">
+        <v>286</v>
+      </c>
+      <c r="C136" t="s">
+        <v>299</v>
+      </c>
+      <c r="D136" t="s">
+        <v>182</v>
+      </c>
+      <c r="F136" t="s">
+        <v>120</v>
+      </c>
+      <c r="G136" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="139" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="I139" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B140" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G140" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="J140" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="K140" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="L140" s="9"/>
+      <c r="M140" s="9"/>
+      <c r="O140" s="9"/>
+    </row>
+    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B141" t="s">
+        <v>301</v>
+      </c>
+      <c r="C141" t="s">
+        <v>302</v>
+      </c>
+      <c r="D141" t="s">
+        <v>133</v>
+      </c>
+      <c r="E141" t="s">
+        <v>119</v>
+      </c>
+      <c r="F141" t="s">
+        <v>120</v>
+      </c>
+      <c r="G141" t="s">
+        <v>303</v>
+      </c>
+      <c r="I141" t="s">
+        <v>307</v>
+      </c>
+      <c r="J141" t="s">
+        <v>308</v>
+      </c>
+      <c r="K141" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>301</v>
+      </c>
+      <c r="C142" t="s">
+        <v>304</v>
+      </c>
+      <c r="D142" t="s">
+        <v>179</v>
+      </c>
+      <c r="F142" t="s">
+        <v>120</v>
+      </c>
+      <c r="G142" t="s">
+        <v>305</v>
+      </c>
+      <c r="I142" t="s">
+        <v>309</v>
+      </c>
+      <c r="J142" t="s">
+        <v>310</v>
+      </c>
+      <c r="K142" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="143" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>301</v>
+      </c>
+      <c r="C143" t="s">
+        <v>259</v>
+      </c>
+      <c r="D143" t="s">
+        <v>260</v>
+      </c>
+      <c r="F143" t="s">
+        <v>120</v>
+      </c>
+      <c r="G143" t="s">
+        <v>306</v>
+      </c>
+      <c r="I143" t="s">
+        <v>311</v>
+      </c>
+      <c r="J143" t="s">
+        <v>312</v>
+      </c>
+      <c r="K143" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="I144" t="s">
+        <v>313</v>
+      </c>
+      <c r="J144" t="s">
+        <v>314</v>
+      </c>
+      <c r="K144" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="145" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I145" t="s">
+        <v>315</v>
+      </c>
+      <c r="J145" t="s">
+        <v>316</v>
+      </c>
+      <c r="K145" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="146" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I146" t="s">
+        <v>317</v>
+      </c>
+      <c r="J146" t="s">
+        <v>318</v>
+      </c>
+      <c r="K146" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="147" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I147" t="s">
+        <v>319</v>
+      </c>
+      <c r="J147" t="s">
+        <v>320</v>
+      </c>
+      <c r="K147" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="149" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I149" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="150" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B150" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E150" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G150" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I150" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="J150" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="K150" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="L150" s="9"/>
+      <c r="M150" s="9"/>
+    </row>
+    <row r="151" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B151" t="s">
+        <v>322</v>
+      </c>
+      <c r="C151" t="s">
+        <v>293</v>
+      </c>
+      <c r="D151" t="s">
+        <v>133</v>
+      </c>
+      <c r="E151" t="s">
+        <v>119</v>
+      </c>
+      <c r="F151" t="s">
+        <v>120</v>
+      </c>
+      <c r="G151" t="s">
+        <v>323</v>
+      </c>
+      <c r="I151" t="s">
+        <v>327</v>
+      </c>
+      <c r="J151" t="s">
+        <v>328</v>
+      </c>
+      <c r="K151" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="152" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B152" t="s">
+        <v>322</v>
+      </c>
+      <c r="C152" t="s">
+        <v>324</v>
+      </c>
+      <c r="D152" t="s">
+        <v>179</v>
+      </c>
+      <c r="F152" t="s">
+        <v>120</v>
+      </c>
+      <c r="G152" t="s">
+        <v>325</v>
+      </c>
+      <c r="I152" t="s">
+        <v>329</v>
+      </c>
+      <c r="J152" t="s">
+        <v>330</v>
+      </c>
+      <c r="K152" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="153" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B153" t="s">
+        <v>322</v>
+      </c>
+      <c r="C153" t="s">
+        <v>259</v>
+      </c>
+      <c r="D153" t="s">
+        <v>260</v>
+      </c>
+      <c r="F153" t="s">
+        <v>120</v>
+      </c>
+      <c r="G153" t="s">
+        <v>326</v>
+      </c>
+      <c r="I153" t="s">
+        <v>331</v>
+      </c>
+      <c r="J153" t="s">
+        <v>332</v>
+      </c>
+      <c r="K153" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="154" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I154" t="s">
+        <v>333</v>
+      </c>
+      <c r="J154" t="s">
+        <v>334</v>
+      </c>
+      <c r="K154" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="155" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I155" t="s">
+        <v>335</v>
+      </c>
+      <c r="J155" t="s">
+        <v>336</v>
+      </c>
+      <c r="K155" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6B5E638-A65D-8F40-B36A-AFDB7D9C80D6}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/01 Requirements/BRD/Feature Mapping.xlsx
+++ b/01 Requirements/BRD/Feature Mapping.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/01 Requirements/BRD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519EB245-EFF9-4D41-8116-2B5280006DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE69E8E1-46D5-E440-97FE-B210F1890C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" activeTab="2" xr2:uid="{E4B2857F-55FC-DA4A-AB72-828E9EE87AFE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" activeTab="4" xr2:uid="{E4B2857F-55FC-DA4A-AB72-828E9EE87AFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Feature Mapping" sheetId="2" r:id="rId2"/>
-    <sheet name="Initiation Tables" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
+    <sheet name="Governance" sheetId="5" r:id="rId3"/>
+    <sheet name="Planning" sheetId="6" r:id="rId4"/>
+    <sheet name="Initiation Tables" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="457">
   <si>
     <t>Req Id</t>
   </si>
@@ -1101,6 +1103,327 @@
   </si>
   <si>
     <t>Owns Project master data</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>archetype_id</t>
+  </si>
+  <si>
+    <t>archetype_code</t>
+  </si>
+  <si>
+    <t>varchar(30)</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>business id like AR12</t>
+  </si>
+  <si>
+    <t>archetype_name</t>
+  </si>
+  <si>
+    <t>varchar(100)</t>
+  </si>
+  <si>
+    <t>Innovation / General / PoC</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>varchar(500)</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>varchar(20)</t>
+  </si>
+  <si>
+    <t>ACTIVE / INACTIVE</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>for future controlled changes</t>
+  </si>
+  <si>
+    <t>varchar(50)</t>
+  </si>
+  <si>
+    <t>admin user</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>Stores archetypes like Innovation, General, PoC.</t>
+  </si>
+  <si>
+    <t>wbs_type_id</t>
+  </si>
+  <si>
+    <t>wbs_type_code</t>
+  </si>
+  <si>
+    <t>GENERAL / QA / VCF / RISKSPHERE</t>
+  </si>
+  <si>
+    <t>wbs_type_name</t>
+  </si>
+  <si>
+    <t>user display name</t>
+  </si>
+  <si>
+    <t>varchar(300)</t>
+  </si>
+  <si>
+    <t>display_sequence</t>
+  </si>
+  <si>
+    <t>dropdown order</t>
+  </si>
+  <si>
+    <t>Stores allowed WBS object types.</t>
+  </si>
+  <si>
+    <t>archetype_wbs_id</t>
+  </si>
+  <si>
+    <t>wbs_code</t>
+  </si>
+  <si>
+    <t>business sequence like 1, 2, 2.1</t>
+  </si>
+  <si>
+    <t>wbs_name</t>
+  </si>
+  <si>
+    <t>varchar(150)</t>
+  </si>
+  <si>
+    <t>Discovery, Design, Development, QA, VCF, AI Risk Assessment</t>
+  </si>
+  <si>
+    <t>FK self</t>
+  </si>
+  <si>
+    <t>level_no</t>
+  </si>
+  <si>
+    <t>1, 2, 3</t>
+  </si>
+  <si>
+    <t>screen ordering</t>
+  </si>
+  <si>
+    <t>is_mandatory</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>default true if always applicable</t>
+  </si>
+  <si>
+    <t>action_required_flag</t>
+  </si>
+  <si>
+    <t>true for types needing action like QA checklist</t>
+  </si>
+  <si>
+    <t>Stores WBS objects for each archetype.</t>
+  </si>
+  <si>
+    <t>supports hierarchy like Design -&gt; AS-IS / TO-BE</t>
+  </si>
+  <si>
+    <t>qa_checklist_id</t>
+  </si>
+  <si>
+    <t>checklist_code</t>
+  </si>
+  <si>
+    <t>checklist_name</t>
+  </si>
+  <si>
+    <t>e.g. Standard Project QA Checklist</t>
+  </si>
+  <si>
+    <t>Stores checklist header/master.</t>
+  </si>
+  <si>
+    <t>qa_checklist_item_id</t>
+  </si>
+  <si>
+    <t>item_code</t>
+  </si>
+  <si>
+    <t>item_name</t>
+  </si>
+  <si>
+    <t>varchar(200)</t>
+  </si>
+  <si>
+    <t>Requirements Documentation Completion, AI Governance Check</t>
+  </si>
+  <si>
+    <t>default_mandatory_flag</t>
+  </si>
+  <si>
+    <t>default behavior</t>
+  </si>
+  <si>
+    <t>Stores individual QA checklist items.</t>
+  </si>
+  <si>
+    <t>QA checklist item master</t>
+  </si>
+  <si>
+    <t>Maps QA checklist items to a specific QA-type WBS object.</t>
+  </si>
+  <si>
+    <t>Mapping QA checklist items to archetype WBS</t>
+  </si>
+  <si>
+    <t>archetype_wbs_qa_map_id</t>
+  </si>
+  <si>
+    <t>mandatory_flag</t>
+  </si>
+  <si>
+    <t>allows override per archetype</t>
+  </si>
+  <si>
+    <t>Role master</t>
+  </si>
+  <si>
+    <t>This should preferably reuse your enterprise/shared role master.</t>
+  </si>
+  <si>
+    <t>role_id</t>
+  </si>
+  <si>
+    <t>role_code</t>
+  </si>
+  <si>
+    <t>ADMIN, PM, COE_HEAD, etc.</t>
+  </si>
+  <si>
+    <t>role_name</t>
+  </si>
+  <si>
+    <t>Action master for access control</t>
+  </si>
+  <si>
+    <t>Stores actions shown on access tab.</t>
+  </si>
+  <si>
+    <t>action_id</t>
+  </si>
+  <si>
+    <t>action_code</t>
+  </si>
+  <si>
+    <t>ADD / EDIT / VIEW / DELETE</t>
+  </si>
+  <si>
+    <t>action_name</t>
+  </si>
+  <si>
+    <t>Archetype WBS access matrix</t>
+  </si>
+  <si>
+    <t>Stores who can do what on each WBS object.</t>
+  </si>
+  <si>
+    <t>archetype_wbs_access_id</t>
+  </si>
+  <si>
+    <t>allowed_flag</t>
+  </si>
+  <si>
+    <t>true / false</t>
+  </si>
+  <si>
+    <t>For future project planning, each project should store selected archetype.</t>
+  </si>
+  <si>
+    <t>project_code</t>
+  </si>
+  <si>
+    <t>Archetype master</t>
+  </si>
+  <si>
+    <t>WBS type master</t>
+  </si>
+  <si>
+    <t>Archetype WBS definition</t>
+  </si>
+  <si>
+    <t>QA checklist master</t>
+  </si>
+  <si>
+    <t>this will be approved project id with code</t>
+  </si>
+  <si>
+    <t>Project Archetype link</t>
+  </si>
+  <si>
+    <t>Governance</t>
+  </si>
+  <si>
+    <t>View archetypes , number of projects associated</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Create Project Archetype</t>
+  </si>
+  <si>
+    <t>View Project Archetypes</t>
+  </si>
+  <si>
+    <t>Archetype ID</t>
+  </si>
+  <si>
+    <t>Object Name</t>
+  </si>
+  <si>
+    <t>Object Parent</t>
+  </si>
+  <si>
+    <t>Object Type ID</t>
+  </si>
+  <si>
+    <t>parent_wbs_id</t>
+  </si>
+  <si>
+    <t>Save as draft</t>
+  </si>
+  <si>
+    <t>Create project WBS against an archetype</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Iniate Project</t>
+  </si>
+  <si>
+    <t>Jira Space Creation Request for SDLC projects</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1495,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1180,12 +1503,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1212,6 +1550,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1621,7 +1963,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D607A7C-00D7-D24E-B0BF-4C14448699DE}">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -1971,15 +2313,6 @@
       <c r="D41" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="2">
-        <v>52</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
@@ -1991,11 +2324,14 @@
       <c r="D42" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G42" s="2">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -2009,10 +2345,7 @@
         <v>20</v>
       </c>
       <c r="G43" s="2">
-        <v>54</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -2026,7 +2359,10 @@
         <v>20</v>
       </c>
       <c r="G44" s="2">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -2040,7 +2376,7 @@
         <v>20</v>
       </c>
       <c r="G45" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -2054,10 +2390,7 @@
         <v>20</v>
       </c>
       <c r="G46" s="2">
-        <v>59</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -2076,6 +2409,9 @@
       <c r="G47" s="2">
         <v>59</v>
       </c>
+      <c r="H47" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C48" s="2" t="s">
@@ -2088,7 +2424,7 @@
         <v>20</v>
       </c>
       <c r="G48" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -2105,7 +2441,7 @@
         <v>20</v>
       </c>
       <c r="G49" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -2119,7 +2455,7 @@
         <v>20</v>
       </c>
       <c r="G50" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -2136,7 +2472,7 @@
         <v>20</v>
       </c>
       <c r="G51" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -2147,7 +2483,7 @@
         <v>100</v>
       </c>
       <c r="G52" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -2161,7 +2497,7 @@
         <v>20</v>
       </c>
       <c r="G53" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -2178,7 +2514,7 @@
         <v>20</v>
       </c>
       <c r="G54" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -2188,44 +2524,102 @@
       <c r="D55" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="G55" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C60" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D61" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="8"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="8"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="8"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="8"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="8"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="8" t="s">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="8"/>
+      <c r="B72" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="8"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="8"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="8"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="8"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" s="8" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="8" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" s="8" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="8" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" s="8" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2238,6 +2632,1234 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EE83712-584E-8149-BABA-DCD228D23EF1}">
+  <dimension ref="B2:H139"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="10"/>
+    <col min="2" max="2" width="23.83203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" s="10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="10" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="10" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="10" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B28" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="12"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B30" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="12"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B31" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B32" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B33" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="10" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" s="12"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B45" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D46" s="12"/>
+      <c r="E46" s="11" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B47" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B48" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B51" s="10" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B53" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B55" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B56" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B57" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B58" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B59" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E59" s="12"/>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B60" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B61" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B64" s="10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B65" s="10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B67" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B68" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E68" s="12"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B69" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B70" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B71" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B72" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B73" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B76" s="10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B77" s="10" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H78" s="10" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B79" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B80" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E80" s="12"/>
+      <c r="H80" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B81" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E81" s="12"/>
+      <c r="H81" s="10" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B82" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B83" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B84" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B85" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B86" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B87" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="D87" s="12"/>
+      <c r="E87" s="13" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B88" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B89" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B90" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B91" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B92" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B93" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B94" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B98" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B99" s="10" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B100" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B101" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E101" s="12"/>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B102" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D102" s="12"/>
+      <c r="E102" s="12"/>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B103" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B104" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D104" s="12"/>
+      <c r="E104" s="12"/>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B105" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B106" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B107" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B108" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B109" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B111" s="10" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B112" s="10" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B113" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B114" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E114" s="12"/>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B115" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E115" s="12"/>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B116" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D116" s="12"/>
+      <c r="E116" s="12"/>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B117" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B118" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B119" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B120" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D120" s="12"/>
+      <c r="E120" s="12"/>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B121" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B122" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B123" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D123" s="12"/>
+      <c r="E123" s="12"/>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B124" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B125" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D125" s="12"/>
+      <c r="E125" s="12"/>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B128" s="10" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B129" s="10" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B131" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B132" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E132" s="12"/>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B133" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E133" s="12"/>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B134" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E134" s="12"/>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B135" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D135" s="12"/>
+      <c r="E135" s="12" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B136" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D136" s="12"/>
+      <c r="E136" s="12"/>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B137" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D137" s="12"/>
+      <c r="E137" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B138" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D138" s="12"/>
+      <c r="E138" s="12"/>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B139" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA0B94D6-C93B-184D-AAD6-CE39B0DC3C33}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F193F0A-FA0B-D541-914E-6262846BAE7B}">
   <dimension ref="B2:O155"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2247,8 +3869,9 @@
     <col min="4" max="4" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="35" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.1640625" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="21.1640625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
@@ -4718,7 +6341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6B5E638-A65D-8F40-B36A-AFDB7D9C80D6}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/01 Requirements/BRD/Feature Mapping.xlsx
+++ b/01 Requirements/BRD/Feature Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/01 Requirements/BRD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE69E8E1-46D5-E440-97FE-B210F1890C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E13AC7-B07C-924E-A3CA-68B83C35EF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" activeTab="4" xr2:uid="{E4B2857F-55FC-DA4A-AB72-828E9EE87AFE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="6" xr2:uid="{E4B2857F-55FC-DA4A-AB72-828E9EE87AFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Planning" sheetId="6" r:id="rId4"/>
     <sheet name="Initiation Tables" sheetId="4" r:id="rId5"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="493">
   <si>
     <t>Req Id</t>
   </si>
@@ -1424,6 +1425,114 @@
   </si>
   <si>
     <t>Jira Space Creation Request for SDLC projects</t>
+  </si>
+  <si>
+    <t>campaign_stage_id</t>
+  </si>
+  <si>
+    <t>Primary key</t>
+  </si>
+  <si>
+    <t>campaign_id</t>
+  </si>
+  <si>
+    <t>FK to CAMPAIGN</t>
+  </si>
+  <si>
+    <t>varchar</t>
+  </si>
+  <si>
+    <t>Example: Stage 1</t>
+  </si>
+  <si>
+    <t>stage_sequence_no</t>
+  </si>
+  <si>
+    <t>Order of stage</t>
+  </si>
+  <si>
+    <t>stage_weightage_pct</t>
+  </si>
+  <si>
+    <t>decimal(5,2)</t>
+  </si>
+  <si>
+    <t>Stage weight</t>
+  </si>
+  <si>
+    <t>min_qualifying_score</t>
+  </si>
+  <si>
+    <t>decimal(8,2) nullable</t>
+  </si>
+  <si>
+    <t>Threshold for progression</t>
+  </si>
+  <si>
+    <t>active_flag</t>
+  </si>
+  <si>
+    <t>char(1)</t>
+  </si>
+  <si>
+    <t>Y/N</t>
+  </si>
+  <si>
+    <t>User id</t>
+  </si>
+  <si>
+    <t>created_on</t>
+  </si>
+  <si>
+    <t>Created timestamp</t>
+  </si>
+  <si>
+    <t>updated_on</t>
+  </si>
+  <si>
+    <t>Updated timestamp</t>
+  </si>
+  <si>
+    <t>varchar (50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigint </t>
+  </si>
+  <si>
+    <t>bigint</t>
+  </si>
+  <si>
+    <t>campaign_evaluator_assignment_id</t>
+  </si>
+  <si>
+    <t>FK to CAMPAIGN_STAGE</t>
+  </si>
+  <si>
+    <t>evaluator_user_id</t>
+  </si>
+  <si>
+    <t>Evaluator employee/user id</t>
+  </si>
+  <si>
+    <t>assignment_status</t>
+  </si>
+  <si>
+    <t>Active / Removed</t>
+  </si>
+  <si>
+    <t>assigned_on</t>
+  </si>
+  <si>
+    <t>Assignment date</t>
+  </si>
+  <si>
+    <t>assigned_by</t>
+  </si>
+  <si>
+    <t>Assigned by moderator</t>
+  </si>
+  <si>
+    <t>varchar (1)</t>
   </si>
 </sst>
 </file>
@@ -1523,7 +1632,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1554,6 +1663,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6395,4 +6506,234 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E773ADDB-2114-7B49-86B7-ADC1F0A16B60}">
+  <dimension ref="B3:D26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>491</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>